--- a/artfynd/A 53422-2024 artfynd.xlsx
+++ b/artfynd/A 53422-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115413234</v>
+        <v>119536117</v>
       </c>
       <c r="B2" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fjällboheden, Vb</t>
+          <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749744</v>
+        <v>749713</v>
       </c>
       <c r="R2" t="n">
-        <v>7216854</v>
+        <v>7216788</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,57 +775,61 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119536117</v>
+        <v>115413234</v>
       </c>
       <c r="B3" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storbäcken, Vb</t>
+          <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749713</v>
+        <v>749744</v>
       </c>
       <c r="R3" t="n">
-        <v>7216788</v>
+        <v>7216854</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 53422-2024 artfynd.xlsx
+++ b/artfynd/A 53422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119536117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115413234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>